--- a/武器系统.xlsx
+++ b/武器系统.xlsx
@@ -4,15 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12780" activeTab="3"/>
+    <workbookView windowWidth="21000" windowHeight="10475" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="武器详细数据" sheetId="1" r:id="rId1"/>
-    <sheet name="符文系统" sheetId="2" r:id="rId2"/>
-    <sheet name="被动图鉴" sheetId="3" r:id="rId3"/>
-    <sheet name="元素反应" sheetId="4" r:id="rId4"/>
-    <sheet name="武器进化" sheetId="5" r:id="rId5"/>
-    <sheet name="天赋系统" sheetId="6" r:id="rId6"/>
+    <sheet name="武器进化" sheetId="5" r:id="rId2"/>
+    <sheet name="武器融合" sheetId="8" r:id="rId3"/>
+    <sheet name="宝石系统" sheetId="2" r:id="rId4"/>
+    <sheet name="被动图鉴" sheetId="3" r:id="rId5"/>
+    <sheet name="元素反应" sheetId="4" r:id="rId6"/>
+    <sheet name="重复获取武器的逻辑" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
   <si>
     <t>行为模式</t>
   </si>
@@ -76,6 +77,9 @@
     <t>图片</t>
   </si>
   <si>
+    <t>技能【联动】</t>
+  </si>
+  <si>
     <t>近战</t>
   </si>
   <si>
@@ -160,6 +164,12 @@
     <t>fairy</t>
   </si>
   <si>
+    <t>武器槽位是否有限，有限的话要设置多少个；【武器点数系统替代武器槽位系统，不同武器占用点数不同】</t>
+  </si>
+  <si>
+    <t>武器与被动道具合并，玩家可随时手动拆分or合并</t>
+  </si>
+  <si>
     <t>符文名称</t>
   </si>
   <si>
@@ -178,12 +188,15 @@
     <t>机制类</t>
   </si>
   <si>
-    <t>-敌人移动速度</t>
-  </si>
-  <si>
     <t>+元素附魔</t>
   </si>
   <si>
+    <t>数值类词条</t>
+  </si>
+  <si>
+    <t>提供给玩家重新锻造roll点的机会</t>
+  </si>
+  <si>
     <t>应该围绕武器构建，而不是与怪物进行元素反应。</t>
   </si>
   <si>
@@ -236,6 +249,18 @@
   </si>
   <si>
     <t>+易伤</t>
+  </si>
+  <si>
+    <t>武器重复获取</t>
+  </si>
+  <si>
+    <t>1.持有多把</t>
+  </si>
+  <si>
+    <t>2.武器升级</t>
+  </si>
+  <si>
+    <t>给玩家多次获取各种武器的机会</t>
   </si>
 </sst>
 </file>
@@ -248,10 +273,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -401,12 +433,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -719,148 +769,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1180,181 +1231,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="5" width="14.1111111111111" customWidth="1"/>
     <col min="7" max="7" width="14.1111111111111" customWidth="1"/>
     <col min="9" max="9" width="14.1111111111111" customWidth="1"/>
+    <col min="16" max="16" width="14.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:15">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="5" customFormat="1" spans="1:16">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="C3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="C5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" hidden="1" spans="1:15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="C7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="C11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="C12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="C13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="B15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="C16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="C19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="B25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="C26" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="C27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="C28" t="s">
-        <v>41</v>
-      </c>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1368,7 +1439,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="13.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="13.8" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="8.66666666666667" style="3"/>
@@ -1378,38 +1480,33 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1418,18 +1515,30 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="13.8"/>
-  <sheetData/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="13.8" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="11.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H9"/>
@@ -1446,7 +1555,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1455,95 +1564,95 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="B2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:8">
+      <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="E2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>51</v>
+      <c r="A3" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>52</v>
+      <c r="A4" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="B7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="B8" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1555,23 +1664,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="13.8"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="13.8"/>
-  <sheetData/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8" outlineLevelRow="2" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
